--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486808_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486808_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.0777</v>
+        <v>6.6941</v>
       </c>
       <c r="E2" t="n">
-        <v>4.574</v>
+        <v>5.0911</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5037</v>
+        <v>1.6031</v>
       </c>
       <c r="G2" t="n">
         <v>6.6004</v>
@@ -610,13 +610,13 @@
         <v>1.9308</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.1198</v>
+        <v>-0.5033</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8554</v>
+        <v>-0.3383</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2644</v>
+        <v>-0.1651</v>
       </c>
       <c r="V2" t="n">
         <v>-0.3683</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.378</v>
+        <v>4.262</v>
       </c>
       <c r="E3" t="n">
-        <v>3.938</v>
+        <v>4.7723</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.5103</v>
       </c>
       <c r="G3" t="n">
         <v>3.1713</v>
@@ -688,13 +688,13 @@
         <v>1.9308</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.0702</v>
+        <v>-0.1862</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9382</v>
+        <v>-0.1039</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.132</v>
+        <v>-0.0823</v>
       </c>
       <c r="V3" t="n">
         <v>-0.6539</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.9568</v>
+        <v>2.3225</v>
       </c>
       <c r="E4" t="n">
-        <v>2.9042</v>
+        <v>2.394</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0527</v>
+        <v>-0.07149999999999999</v>
       </c>
       <c r="G4" t="n">
         <v>3.1073</v>
@@ -766,13 +766,13 @@
         <v>1.7377</v>
       </c>
       <c r="S4" t="n">
-        <v>1.048</v>
+        <v>0.4137</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7718</v>
+        <v>0.2617</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2762</v>
+        <v>0.152</v>
       </c>
       <c r="V4" t="n">
         <v>-0.0401</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1474</v>
+        <v>1.0522</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0636</v>
+        <v>0.6673</v>
       </c>
       <c r="F5" t="n">
-        <v>0.211</v>
+        <v>0.3848</v>
       </c>
       <c r="G5" t="n">
         <v>0.3945</v>
@@ -844,13 +844,13 @@
         <v>2.1239</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4635</v>
+        <v>0.4412</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9382</v>
+        <v>-0.2073</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4747</v>
+        <v>0.6486</v>
       </c>
       <c r="V5" t="n">
         <v>-0.9421</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2281</v>
+        <v>-0.2805</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2193</v>
+        <v>0.06759999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4474</v>
+        <v>-0.3481</v>
       </c>
       <c r="G6" t="n">
         <v>-0.6225000000000001</v>
@@ -922,13 +922,13 @@
         <v>1.1585</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0443</v>
+        <v>-0.09660000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3032</v>
+        <v>0.1515</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3475</v>
+        <v>-0.2481</v>
       </c>
       <c r="V6" t="n">
         <v>0.2455</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8299</v>
+        <v>-0.4148</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6093</v>
+        <v>0.9747</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.4392</v>
+        <v>-1.3895</v>
       </c>
       <c r="G7" t="n">
         <v>-0.3044</v>
@@ -1000,13 +1000,13 @@
         <v>1.1585</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9875</v>
+        <v>-0.5724</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3311</v>
+        <v>0.0344</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6564</v>
+        <v>-0.6067</v>
       </c>
       <c r="V7" t="n">
         <v>-0.6965</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. LAGUNA RODRIGUEZ</t>
+          <t>D. SANCHEZ PEREZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.3527</v>
+        <v>-0.7963</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.9989</v>
+        <v>-0.2988</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6462</v>
+        <v>-0.4975</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.3373</v>
+        <v>0.7072000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.9794</v>
+        <v>-1.3794</v>
       </c>
       <c r="I8" t="n">
-        <v>0.642</v>
+        <v>2.0866</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.1711</v>
+        <v>1.6599</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.2548</v>
+        <v>-0.1374</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0837</v>
+        <v>1.7973</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.1662</v>
+        <v>-0.9527</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.7246</v>
+        <v>-1.242</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5583</v>
+        <v>0.2893</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1931</v>
+        <v>-0.5792</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9654</v>
+        <v>-1.9308</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1585</v>
+        <v>1.3515</v>
       </c>
       <c r="S8" t="n">
-        <v>1.3628</v>
+        <v>0.3034</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1377</v>
+        <v>-0.0279</v>
       </c>
       <c r="U8" t="n">
-        <v>1.2252</v>
+        <v>0.3313</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.5712</v>
+        <v>-1.2277</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5712</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. SANCHEZ PEREZ</t>
+          <t>M. LAGUNA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.4142</v>
+        <v>-2.3086</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7675999999999999</v>
+        <v>-2.3091</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6465</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7072000000000001</v>
+        <v>-2.3373</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.3794</v>
+        <v>-2.9794</v>
       </c>
       <c r="I9" t="n">
-        <v>2.0866</v>
+        <v>0.642</v>
       </c>
       <c r="J9" t="n">
-        <v>1.6599</v>
+        <v>-1.1711</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.1374</v>
+        <v>-1.2548</v>
       </c>
       <c r="L9" t="n">
-        <v>1.7973</v>
+        <v>0.0837</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.9527</v>
+        <v>-1.1662</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.242</v>
+        <v>-1.7246</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2893</v>
+        <v>0.5583</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.5792</v>
+        <v>0.1931</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9308</v>
+        <v>-0.9654</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3515</v>
+        <v>1.1585</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3145</v>
+        <v>0.4069</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4968</v>
+        <v>-0.1726</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1823</v>
+        <v>0.5795</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2277</v>
+        <v>-0.5712</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2277</v>
+        <v>-0.5712</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.4349</v>
+        <v>-3.6155</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.3185</v>
+        <v>-2.5736</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.1164</v>
+        <v>-1.0419</v>
       </c>
       <c r="G10" t="n">
         <v>-2.3741</v>
@@ -1234,13 +1234,13 @@
         <v>0.7723</v>
       </c>
       <c r="S10" t="n">
-        <v>0.7115</v>
+        <v>0.5309</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5515</v>
+        <v>0.2964</v>
       </c>
       <c r="U10" t="n">
-        <v>0.16</v>
+        <v>0.2345</v>
       </c>
       <c r="V10" t="n">
         <v>-0.6138</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.8465</v>
+        <v>-5.9096</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.6235</v>
+        <v>-3.7611</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.223</v>
+        <v>-2.1485</v>
       </c>
       <c r="G11" t="n">
         <v>-3.3755</v>
@@ -1312,13 +1312,13 @@
         <v>1.1585</v>
       </c>
       <c r="S11" t="n">
-        <v>1.4285</v>
+        <v>0.3654</v>
       </c>
       <c r="T11" t="n">
-        <v>1.5166</v>
+        <v>0.379</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0881</v>
+        <v>-0.0136</v>
       </c>
       <c r="V11" t="n">
         <v>-2.1271</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4536000000000016</v>
+        <v>1.0055</v>
       </c>
       <c r="E12" t="n">
-        <v>4.472700000000001</v>
+        <v>5.024400000000003</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.0189</v>
+        <v>-4.018800000000001</v>
       </c>
       <c r="G12" t="n">
         <v>4.966899999999997</v>
@@ -1390,13 +1390,13 @@
         <v>14.481</v>
       </c>
       <c r="S12" t="n">
-        <v>0.5510000000000002</v>
+        <v>1.103</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2789000000000001</v>
+        <v>0.273</v>
       </c>
       <c r="U12" t="n">
-        <v>0.8300000000000001</v>
+        <v>0.8300999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>-6.995200000000001</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.5841</v>
+        <v>4.5497</v>
       </c>
       <c r="E13" t="n">
-        <v>4.4818</v>
+        <v>4.1715</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1024</v>
+        <v>0.3781</v>
       </c>
       <c r="G13" t="n">
         <v>1.2255</v>
@@ -1468,13 +1468,13 @@
         <v>1.7377</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2206</v>
+        <v>-0.2551</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0004</v>
+        <v>-0.3106</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2203</v>
+        <v>0.0555</v>
       </c>
       <c r="V13" t="n">
         <v>1.8415</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. CASTELANOS POLA</t>
+          <t>N. CEBRIAN HERNANDEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.4847</v>
+        <v>2.5143</v>
       </c>
       <c r="E14" t="n">
-        <v>1.447</v>
+        <v>2.7944</v>
       </c>
       <c r="F14" t="n">
-        <v>1.0378</v>
+        <v>-0.2801</v>
       </c>
       <c r="G14" t="n">
-        <v>1.0805</v>
+        <v>2.5391</v>
       </c>
       <c r="H14" t="n">
-        <v>2.3171</v>
+        <v>0.8549</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.2366</v>
+        <v>1.6842</v>
       </c>
       <c r="J14" t="n">
-        <v>2.0953</v>
+        <v>4.4924</v>
       </c>
       <c r="K14" t="n">
-        <v>3.3521</v>
+        <v>1.4766</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.2569</v>
+        <v>3.0158</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.0148</v>
+        <v>-1.9533</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.0351</v>
+        <v>-0.6217</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0203</v>
+        <v>-1.3316</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.3862</v>
+        <v>0.7723</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.9308</v>
+        <v>-0.9654</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5446</v>
+        <v>1.7377</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5627</v>
+        <v>-0.4689</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0548</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5079</v>
+        <v>0.2211</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2277</v>
+        <v>-0.3282</v>
       </c>
       <c r="W14" t="n">
-        <v>1.2277</v>
+        <v>-0.0426</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>N. CEBRIAN HERNANDEZ</t>
+          <t>A. CASTELANOS POLA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.7255</v>
+        <v>2.1634</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3807</v>
+        <v>1.1367</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.6552</v>
+        <v>1.0267</v>
       </c>
       <c r="G15" t="n">
-        <v>2.5391</v>
+        <v>1.0805</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8549</v>
+        <v>2.3171</v>
       </c>
       <c r="I15" t="n">
-        <v>1.6842</v>
+        <v>-1.2366</v>
       </c>
       <c r="J15" t="n">
-        <v>4.4924</v>
+        <v>2.0953</v>
       </c>
       <c r="K15" t="n">
-        <v>1.4766</v>
+        <v>3.3521</v>
       </c>
       <c r="L15" t="n">
-        <v>3.0158</v>
+        <v>-1.2569</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.9533</v>
+        <v>-1.0148</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6217</v>
+        <v>-1.0351</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.3316</v>
+        <v>0.0203</v>
       </c>
       <c r="P15" t="n">
-        <v>0.7723</v>
+        <v>-0.3862</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9654</v>
+        <v>-1.9308</v>
       </c>
       <c r="R15" t="n">
-        <v>1.7377</v>
+        <v>1.5446</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.2577</v>
+        <v>0.2414</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.1036</v>
+        <v>-0.2554</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.154</v>
+        <v>0.4968</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.3282</v>
+        <v>1.2277</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.0426</v>
+        <v>1.2277</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.6525</v>
+        <v>1.6691</v>
       </c>
       <c r="E16" t="n">
-        <v>2.5801</v>
+        <v>2.3733</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.9276</v>
+        <v>-0.7040999999999999</v>
       </c>
       <c r="G16" t="n">
         <v>-2.2897</v>
@@ -1702,13 +1702,13 @@
         <v>0.7723</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4522</v>
+        <v>0.4688</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5238</v>
+        <v>0.317</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0716</v>
+        <v>0.1519</v>
       </c>
       <c r="V16" t="n">
         <v>3.6831</v>
@@ -1735,10 +1735,10 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0144</v>
+        <v>0.1925</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2692</v>
+        <v>1.4761</v>
       </c>
       <c r="F17" t="n">
         <v>-1.2836</v>
@@ -1780,10 +1780,10 @@
         <v>0.9654</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1655</v>
+        <v>0.3724</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1657</v>
+        <v>0.0412</v>
       </c>
       <c r="U17" t="n">
         <v>0.3312</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.8923</v>
+        <v>-0.5228</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3403</v>
+        <v>0.5471</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.2326</v>
+        <v>-1.0699</v>
       </c>
       <c r="G18" t="n">
         <v>-1.1945</v>
@@ -1858,13 +1858,13 @@
         <v>1.3515</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3696</v>
+        <v>-0</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5795</v>
+        <v>-0.3726</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2099</v>
+        <v>0.3726</v>
       </c>
       <c r="V18" t="n">
         <v>0.2856</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.3732</v>
+        <v>-0.9361</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.1253</v>
+        <v>-1.815</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7521</v>
+        <v>0.8789</v>
       </c>
       <c r="G19" t="n">
         <v>-0.5817</v>
@@ -1936,13 +1936,13 @@
         <v>1.5446</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7335</v>
+        <v>-0.2964</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6898</v>
+        <v>-0.3796</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0437</v>
+        <v>0.08309999999999999</v>
       </c>
       <c r="V19" t="n">
         <v>0.3282</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.1444</v>
+        <v>-2.1651</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.075</v>
+        <v>-1.9716</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0694</v>
+        <v>-0.1935</v>
       </c>
       <c r="G20" t="n">
         <v>-1.4825</v>
@@ -2014,13 +2014,13 @@
         <v>0.7723</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4966</v>
+        <v>0.4758</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2481</v>
+        <v>0.3516</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2484</v>
+        <v>0.1243</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.3337</v>
+        <v>-2.9694</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.6141</v>
+        <v>-2.338</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7197</v>
+        <v>-0.6314</v>
       </c>
       <c r="G21" t="n">
         <v>-2.2633</v>
@@ -2092,13 +2092,13 @@
         <v>1.1585</v>
       </c>
       <c r="S21" t="n">
-        <v>0.9875</v>
+        <v>0.3517</v>
       </c>
       <c r="T21" t="n">
-        <v>1.1029</v>
+        <v>0.379</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1155</v>
+        <v>-0.0272</v>
       </c>
       <c r="V21" t="n">
         <v>-0.2856</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.1426</v>
+        <v>-3.5703</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.6658</v>
+        <v>-2.3556</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.4767</v>
+        <v>-1.2147</v>
       </c>
       <c r="G22" t="n">
         <v>-2.4343</v>
@@ -2170,13 +2170,13 @@
         <v>0.9654</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6344</v>
+        <v>-0.062</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2208</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4135</v>
+        <v>-0.1515</v>
       </c>
       <c r="V22" t="n">
         <v>0.8568</v>
@@ -2203,16 +2203,16 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4537999999999998</v>
+        <v>0.9252999999999996</v>
       </c>
       <c r="E23" t="n">
         <v>4.018899999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.472499999999999</v>
+        <v>-3.0936</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.967</v>
+        <v>-4.967000000000001</v>
       </c>
       <c r="H23" t="n">
         <v>7.2408</v>
@@ -2248,13 +2248,13 @@
         <v>12.55</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5513000000000001</v>
+        <v>0.8277000000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8301999999999999</v>
+        <v>-0.83</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2788</v>
+        <v>1.6578</v>
       </c>
       <c r="V23" t="n">
         <v>6.9953</v>
